--- a/sheets/personal-finance/personal-balance-sheet/personal-balance-sheet.xlsx
+++ b/sheets/personal-finance/personal-balance-sheet/personal-balance-sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\personal-finance\personal-balance-sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60DA93F-C620-4847-81A5-6C7D03CE1156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C4183B-8C19-44DC-9D6A-14E120C8E31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Balance Sheet" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="97">
-  <si>
-    <t>Personal Balance Sheet (Current Quarter)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>Line Item</t>
   </si>
@@ -290,18 +287,6 @@
   </si>
   <si>
     <t>Fixed Assets</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>QoQ Change</t>
-  </si>
-  <si>
-    <t>Current Liabilities</t>
-  </si>
-  <si>
-    <t>Long-Term Liabilities</t>
   </si>
   <si>
     <t>Personal Balance Sheet with Financial Ratios</t>
@@ -335,11 +320,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,13 +346,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -417,6 +396,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -424,11 +417,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6B2D3E"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -443,6 +431,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD0D8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -484,10 +478,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -498,71 +493,158 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8A8A0"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8C88A"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC8D8B0"/>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8A8A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8C88A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC8D8B0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -601,33 +683,81 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Net Worth by Quarter</a:t>
+              <a:rPr lang="en-US" sz="1800" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Net Worth</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="1"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -643,14 +773,83 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
-          <c:cat>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="38100" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="1"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.5021216097987753E-2"/>
+                  <c:y val="0.48569444444444437"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
             <c:strRef>
               <c:f>Dashboard!$A$4:$A$11</c:f>
               <c:strCache>
@@ -681,8 +880,8 @@
                 </c:pt>
               </c:strCache>
             </c:strRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Dashboard!$B$4:$B$11</c:f>
               <c:numCache>
@@ -714,11 +913,11 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FA40-4BFC-BA92-BEC953A37F75}"/>
+              <c16:uniqueId val="{00000000-75E7-48AA-9F66-22F5E19C9EE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -730,71 +929,177 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="1956770064"/>
+        <c:axId val="1956772464"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1956770064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1956772464"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="1956772464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="200000"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Net Worth</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1956770064"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -807,34 +1112,82 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Asset Composition by Quarter</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="1"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -850,11 +1203,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$A$15:$A$22</c:f>
@@ -922,7 +1279,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F7E6-46FF-A73F-16DA851D1818}"/>
+              <c16:uniqueId val="{00000000-02DD-42DE-8F92-99FA331E6492}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -941,11 +1298,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$A$15:$A$22</c:f>
@@ -1013,7 +1374,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F7E6-46FF-A73F-16DA851D1818}"/>
+              <c16:uniqueId val="{00000001-02DD-42DE-8F92-99FA331E6492}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1032,11 +1393,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$A$15:$A$22</c:f>
@@ -1104,7 +1469,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F7E6-46FF-A73F-16DA851D1818}"/>
+              <c16:uniqueId val="{00000002-02DD-42DE-8F92-99FA331E6492}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1117,70 +1482,185 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
+        <c:overlap val="100"/>
+        <c:axId val="1956837264"/>
+        <c:axId val="1881833696"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="1956837264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1881833696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="1881833696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Dollars</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1956837264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="1"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1193,26 +1673,68 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Current Financial Ratios</a:t>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Current Value</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1220,13 +1742,13 @@
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$40</c:f>
+              <c:f>Dashboard!$B$24</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1236,14 +1758,97 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$41:$A$46</c:f>
+              <c:f>Dashboard!$A$25:$A$30</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1269,7 +1874,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$41:$B$46</c:f>
+              <c:f>Dashboard!$B$25:$B$30</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1296,65 +1901,123 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8CB6-43A2-87AC-BD392BE312EA}"/>
+              <c16:uniqueId val="{00000000-4E03-430E-8053-C47E7E0B1C1B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
+        <c:overlap val="-25"/>
+        <c:axId val="2024966160"/>
+        <c:axId val="2024962320"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="2024966160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2024962320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="2024962320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:crossAx val="2024966160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1363,208 +2026,1636 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>QoQ Change by Section</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Dashboard!$B$64</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>QoQ Change</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="1"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Dashboard!$A$65:$A$69</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Current Assets</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Investment Assets</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Fixed Assets</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Current Liabilities</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Long-Term Liabilities</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Dashboard!$B$65:$B$69</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>420</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3235</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5037</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-34</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-2213</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0F93-465A-A3C3-1EF41507C89C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Change ($)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="220">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>367778</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6480000" cy="4320000"/>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="8" name="Chart 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7517D052-7B38-8EA0-AB8D-97461CFC3D16}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1581,21 +3672,26 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>372717</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>157161</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6480000" cy="4320000"/>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5C02C19-0286-A7B8-251F-A4599DB74562}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1612,21 +3708,26 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5760000" cy="3600000"/>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="10" name="Chart 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EE8D924-2DF1-4FBE-7647-00D948AD0D40}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1643,38 +3744,7 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5760000" cy="3600000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1963,47 +4033,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="5">
+        <v>4820</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7">
-        <v>4820</v>
+      <c r="B4" s="5">
+        <v>13204</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
-        <v>13204</v>
+      <c r="B5" s="5">
+        <v>3414</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2011,62 +4083,62 @@
         <v>6</v>
       </c>
       <c r="B6" s="7">
-        <v>3414</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+        <f>SUM(B3:B5)</f>
+        <v>21438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="9">
-        <f>SUM(B4:B6)</f>
-        <v>21438</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="5">
+        <v>35625</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7">
-        <v>35625</v>
+      <c r="B9" s="5">
+        <v>72764</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="7">
-        <v>72764</v>
+      <c r="B10" s="5">
+        <v>29834</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="7">
-        <v>29834</v>
+      <c r="B11" s="5">
+        <v>5865</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7">
-        <v>5865</v>
+      <c r="B12" s="5">
+        <v>7395</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7">
-        <v>7395</v>
+      <c r="B13" s="5">
+        <v>2927</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2074,38 +4146,38 @@
         <v>14</v>
       </c>
       <c r="B14" s="7">
-        <v>2927</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+        <f>SUM(B8:B13)</f>
+        <v>154410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="9">
-        <f>SUM(B9:B14)</f>
-        <v>154410</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="5">
+        <v>289539</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="7">
-        <v>289539</v>
+      <c r="B17" s="5">
+        <v>12989</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="7">
-        <v>12989</v>
+      <c r="B18" s="5">
+        <v>7506</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2113,47 +4185,47 @@
         <v>19</v>
       </c>
       <c r="B19" s="7">
-        <v>7506</v>
+        <f>SUM(B16:B18)</f>
+        <v>310034</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="9">
-        <f>SUM(B17:B19)</f>
-        <v>310034</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="7">
+        <f>B6+B14+B19</f>
+        <v>485882</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="9">
-        <f>B7+B15+B20</f>
-        <v>485882</v>
-      </c>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="5">
+        <v>2703</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="7">
-        <v>2703</v>
+      <c r="B23" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="7">
-        <v>0</v>
+      <c r="B24" s="5">
+        <v>870</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2161,80 +4233,72 @@
         <v>25</v>
       </c>
       <c r="B25" s="7">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <f>SUM(B22:B24)</f>
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="9">
-        <f>SUM(B23:B25)</f>
-        <v>3573</v>
-      </c>
+      <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" s="5">
+        <v>142700</v>
+      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="7">
-        <v>142700</v>
+      <c r="B28" s="5">
+        <v>15718</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="7">
-        <v>15718</v>
+      <c r="B29" s="5">
+        <v>6369</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="7">
-        <v>6369</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" s="23" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="B31" s="22">
+        <f>SUM(B27:B30)</f>
+        <v>164787</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" s="23" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="9">
-        <f>SUM(B28:B31)</f>
-        <v>164787</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="B32" s="22">
+        <f>B25+B31</f>
+        <v>168360</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="23" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="9">
-        <f>B26+B32</f>
-        <v>168360</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="12">
-        <f>B21-B33</f>
+      <c r="B33" s="10">
+        <f>B20-B32</f>
         <v>317522</v>
       </c>
     </row>
@@ -2255,7 +4319,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2267,174 +4331,174 @@
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5">
+        <v>4475</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4505</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4577</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4605</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4659</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4772</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4782</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7">
-        <v>4475</v>
-      </c>
-      <c r="C4" s="7">
-        <v>4505</v>
-      </c>
-      <c r="D4" s="7">
-        <v>4577</v>
-      </c>
-      <c r="E4" s="7">
-        <v>4605</v>
-      </c>
-      <c r="F4" s="7">
-        <v>4659</v>
-      </c>
-      <c r="G4" s="7">
-        <v>4772</v>
-      </c>
-      <c r="H4" s="7">
-        <v>4782</v>
-      </c>
-      <c r="I4" s="7">
-        <v>4820</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="5">
+        <v>12101</v>
+      </c>
+      <c r="C5" s="5">
+        <v>12127</v>
+      </c>
+      <c r="D5" s="5">
+        <v>12173</v>
+      </c>
+      <c r="E5" s="5">
+        <v>12424</v>
+      </c>
+      <c r="F5" s="5">
+        <v>12728</v>
+      </c>
+      <c r="G5" s="5">
+        <v>12830</v>
+      </c>
+      <c r="H5" s="5">
+        <v>12891</v>
+      </c>
+      <c r="I5" s="5">
+        <v>13204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
-        <v>12101</v>
-      </c>
-      <c r="C5" s="7">
-        <v>12127</v>
-      </c>
-      <c r="D5" s="7">
-        <v>12173</v>
-      </c>
-      <c r="E5" s="7">
-        <v>12424</v>
-      </c>
-      <c r="F5" s="7">
-        <v>12728</v>
-      </c>
-      <c r="G5" s="7">
-        <v>12830</v>
-      </c>
-      <c r="H5" s="7">
-        <v>12891</v>
-      </c>
-      <c r="I5" s="7">
-        <v>13204</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="5">
+        <v>2999</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3044</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3090</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3139</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3211</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3288</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3345</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7">
-        <v>2999</v>
-      </c>
-      <c r="C6" s="7">
-        <v>3044</v>
-      </c>
-      <c r="D6" s="7">
-        <v>3090</v>
-      </c>
-      <c r="E6" s="7">
-        <v>3139</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3211</v>
-      </c>
-      <c r="G6" s="7">
-        <v>3288</v>
-      </c>
-      <c r="H6" s="7">
-        <v>3345</v>
-      </c>
-      <c r="I6" s="7">
-        <v>3414</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <f t="shared" ref="B7:I7" si="0">SUM(B4:B6)</f>
         <v>19575</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <f t="shared" si="0"/>
         <v>19676</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <f t="shared" si="0"/>
         <v>19840</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>20168</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>20598</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="12">
         <f t="shared" si="0"/>
         <v>20890</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="12">
         <f t="shared" si="0"/>
         <v>21018</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="12">
         <f t="shared" si="0"/>
         <v>21438</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>8</v>
+      <c r="A8" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2446,219 +4510,219 @@
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <v>30638</v>
+      </c>
+      <c r="C9" s="5">
+        <v>31437</v>
+      </c>
+      <c r="D9" s="5">
+        <v>32090</v>
+      </c>
+      <c r="E9" s="5">
+        <v>32593</v>
+      </c>
+      <c r="F9" s="5">
+        <v>33136</v>
+      </c>
+      <c r="G9" s="5">
+        <v>34238</v>
+      </c>
+      <c r="H9" s="5">
+        <v>35180</v>
+      </c>
+      <c r="I9" s="5">
+        <v>35625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7">
-        <v>30638</v>
-      </c>
-      <c r="C9" s="7">
-        <v>31437</v>
-      </c>
-      <c r="D9" s="7">
-        <v>32090</v>
-      </c>
-      <c r="E9" s="7">
-        <v>32593</v>
-      </c>
-      <c r="F9" s="7">
-        <v>33136</v>
-      </c>
-      <c r="G9" s="7">
-        <v>34238</v>
-      </c>
-      <c r="H9" s="7">
-        <v>35180</v>
-      </c>
-      <c r="I9" s="7">
-        <v>35625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="5">
+        <v>63206</v>
+      </c>
+      <c r="C10" s="5">
+        <v>64266</v>
+      </c>
+      <c r="D10" s="5">
+        <v>66021</v>
+      </c>
+      <c r="E10" s="5">
+        <v>67440</v>
+      </c>
+      <c r="F10" s="5">
+        <v>68569</v>
+      </c>
+      <c r="G10" s="5">
+        <v>69613</v>
+      </c>
+      <c r="H10" s="5">
+        <v>71317</v>
+      </c>
+      <c r="I10" s="5">
+        <v>72764</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="7">
-        <v>63206</v>
-      </c>
-      <c r="C10" s="7">
-        <v>64266</v>
-      </c>
-      <c r="D10" s="7">
-        <v>66021</v>
-      </c>
-      <c r="E10" s="7">
-        <v>67440</v>
-      </c>
-      <c r="F10" s="7">
-        <v>68569</v>
-      </c>
-      <c r="G10" s="7">
-        <v>69613</v>
-      </c>
-      <c r="H10" s="7">
-        <v>71317</v>
-      </c>
-      <c r="I10" s="7">
-        <v>72764</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="B11" s="5">
+        <v>24410</v>
+      </c>
+      <c r="C11" s="5">
+        <v>25079</v>
+      </c>
+      <c r="D11" s="5">
+        <v>25844</v>
+      </c>
+      <c r="E11" s="5">
+        <v>26654</v>
+      </c>
+      <c r="F11" s="5">
+        <v>27337</v>
+      </c>
+      <c r="G11" s="5">
+        <v>28271</v>
+      </c>
+      <c r="H11" s="5">
+        <v>28904</v>
+      </c>
+      <c r="I11" s="5">
+        <v>29834</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="7">
-        <v>24410</v>
-      </c>
-      <c r="C11" s="7">
-        <v>25079</v>
-      </c>
-      <c r="D11" s="7">
-        <v>25844</v>
-      </c>
-      <c r="E11" s="7">
-        <v>26654</v>
-      </c>
-      <c r="F11" s="7">
-        <v>27337</v>
-      </c>
-      <c r="G11" s="7">
-        <v>28271</v>
-      </c>
-      <c r="H11" s="7">
-        <v>28904</v>
-      </c>
-      <c r="I11" s="7">
-        <v>29834</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="5">
+        <v>5080</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5235</v>
+      </c>
+      <c r="D12" s="5">
+        <v>5304</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5433</v>
+      </c>
+      <c r="F12" s="5">
+        <v>5557</v>
+      </c>
+      <c r="G12" s="5">
+        <v>5626</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5734</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5865</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7">
-        <v>5080</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5235</v>
-      </c>
-      <c r="D12" s="7">
-        <v>5304</v>
-      </c>
-      <c r="E12" s="7">
-        <v>5433</v>
-      </c>
-      <c r="F12" s="7">
-        <v>5557</v>
-      </c>
-      <c r="G12" s="7">
-        <v>5626</v>
-      </c>
-      <c r="H12" s="7">
-        <v>5734</v>
-      </c>
-      <c r="I12" s="7">
-        <v>5865</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="B13" s="5">
+        <v>6182</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6245</v>
+      </c>
+      <c r="D13" s="5">
+        <v>6399</v>
+      </c>
+      <c r="E13" s="5">
+        <v>6529</v>
+      </c>
+      <c r="F13" s="5">
+        <v>6754</v>
+      </c>
+      <c r="G13" s="5">
+        <v>6965</v>
+      </c>
+      <c r="H13" s="5">
+        <v>7179</v>
+      </c>
+      <c r="I13" s="5">
+        <v>7395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7">
-        <v>6182</v>
-      </c>
-      <c r="C13" s="7">
-        <v>6245</v>
-      </c>
-      <c r="D13" s="7">
-        <v>6399</v>
-      </c>
-      <c r="E13" s="7">
-        <v>6529</v>
-      </c>
-      <c r="F13" s="7">
-        <v>6754</v>
-      </c>
-      <c r="G13" s="7">
-        <v>6965</v>
-      </c>
-      <c r="H13" s="7">
-        <v>7179</v>
-      </c>
-      <c r="I13" s="7">
-        <v>7395</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="5">
+        <v>2590</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2663</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2696</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2732</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2785</v>
+      </c>
+      <c r="G14" s="5">
+        <v>2830</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2861</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="7">
-        <v>2590</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2663</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2696</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2732</v>
-      </c>
-      <c r="F14" s="7">
-        <v>2785</v>
-      </c>
-      <c r="G14" s="7">
-        <v>2830</v>
-      </c>
-      <c r="H14" s="7">
-        <v>2861</v>
-      </c>
-      <c r="I14" s="7">
-        <v>2927</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="14">
+      <c r="B15" s="12">
         <f t="shared" ref="B15:I15" si="1">SUM(B9:B14)</f>
         <v>132106</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="12">
         <f t="shared" si="1"/>
         <v>134925</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <f t="shared" si="1"/>
         <v>138354</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <f t="shared" si="1"/>
         <v>141381</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="12">
         <f t="shared" si="1"/>
         <v>144138</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="12">
         <f t="shared" si="1"/>
         <v>147543</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="12">
         <f t="shared" si="1"/>
         <v>151175</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="12">
         <f t="shared" si="1"/>
         <v>154410</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>16</v>
+      <c r="A16" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2670,169 +4734,169 @@
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
+        <v>269335</v>
+      </c>
+      <c r="C17" s="5">
+        <v>269327</v>
+      </c>
+      <c r="D17" s="5">
+        <v>270385</v>
+      </c>
+      <c r="E17" s="5">
+        <v>276106</v>
+      </c>
+      <c r="F17" s="5">
+        <v>279201</v>
+      </c>
+      <c r="G17" s="5">
+        <v>281889</v>
+      </c>
+      <c r="H17" s="5">
+        <v>284273</v>
+      </c>
+      <c r="I17" s="5">
+        <v>289539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="7">
-        <v>269335</v>
-      </c>
-      <c r="C17" s="7">
-        <v>269327</v>
-      </c>
-      <c r="D17" s="7">
-        <v>270385</v>
-      </c>
-      <c r="E17" s="7">
-        <v>276106</v>
-      </c>
-      <c r="F17" s="7">
-        <v>279201</v>
-      </c>
-      <c r="G17" s="7">
-        <v>281889</v>
-      </c>
-      <c r="H17" s="7">
-        <v>284273</v>
-      </c>
-      <c r="I17" s="7">
-        <v>289539</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="B18" s="5">
+        <v>15021</v>
+      </c>
+      <c r="C18" s="5">
+        <v>14722</v>
+      </c>
+      <c r="D18" s="5">
+        <v>14414</v>
+      </c>
+      <c r="E18" s="5">
+        <v>14261</v>
+      </c>
+      <c r="F18" s="5">
+        <v>13840</v>
+      </c>
+      <c r="G18" s="5">
+        <v>13578</v>
+      </c>
+      <c r="H18" s="5">
+        <v>13388</v>
+      </c>
+      <c r="I18" s="5">
+        <v>12989</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="7">
-        <v>15021</v>
-      </c>
-      <c r="C18" s="7">
-        <v>14722</v>
-      </c>
-      <c r="D18" s="7">
-        <v>14414</v>
-      </c>
-      <c r="E18" s="7">
-        <v>14261</v>
-      </c>
-      <c r="F18" s="7">
-        <v>13840</v>
-      </c>
-      <c r="G18" s="7">
-        <v>13578</v>
-      </c>
-      <c r="H18" s="7">
-        <v>13388</v>
-      </c>
-      <c r="I18" s="7">
-        <v>12989</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="5">
+        <v>6854</v>
+      </c>
+      <c r="C19" s="5">
+        <v>6913</v>
+      </c>
+      <c r="D19" s="5">
+        <v>7024</v>
+      </c>
+      <c r="E19" s="5">
+        <v>7115</v>
+      </c>
+      <c r="F19" s="5">
+        <v>7204</v>
+      </c>
+      <c r="G19" s="5">
+        <v>7258</v>
+      </c>
+      <c r="H19" s="5">
+        <v>7336</v>
+      </c>
+      <c r="I19" s="5">
+        <v>7506</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="7">
-        <v>6854</v>
-      </c>
-      <c r="C19" s="7">
-        <v>6913</v>
-      </c>
-      <c r="D19" s="7">
-        <v>7024</v>
-      </c>
-      <c r="E19" s="7">
-        <v>7115</v>
-      </c>
-      <c r="F19" s="7">
-        <v>7204</v>
-      </c>
-      <c r="G19" s="7">
-        <v>7258</v>
-      </c>
-      <c r="H19" s="7">
-        <v>7336</v>
-      </c>
-      <c r="I19" s="7">
-        <v>7506</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="14">
+      <c r="B20" s="12">
         <f t="shared" ref="B20:I20" si="2">SUM(B17:B19)</f>
         <v>291210</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <f t="shared" si="2"/>
         <v>290962</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <f t="shared" si="2"/>
         <v>291823</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <f t="shared" si="2"/>
         <v>297482</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <f t="shared" si="2"/>
         <v>300245</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="12">
         <f t="shared" si="2"/>
         <v>302725</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="12">
         <f t="shared" si="2"/>
         <v>304997</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="12">
         <f t="shared" si="2"/>
         <v>310034</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="14">
+      <c r="A21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12">
         <f t="shared" ref="B21:I21" si="3">B7+B15+B20</f>
         <v>442891</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="12">
         <f t="shared" si="3"/>
         <v>445563</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="12">
         <f t="shared" si="3"/>
         <v>450017</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <f t="shared" si="3"/>
         <v>459031</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <f t="shared" si="3"/>
         <v>464981</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="12">
         <f t="shared" si="3"/>
         <v>471158</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="12">
         <f t="shared" si="3"/>
         <v>477190</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="12">
         <f t="shared" si="3"/>
         <v>485882</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>22</v>
+      <c r="A22" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2844,132 +4908,132 @@
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5">
+        <v>3142</v>
+      </c>
+      <c r="C23" s="5">
+        <v>3055</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2976</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2890</v>
+      </c>
+      <c r="F23" s="5">
+        <v>2814</v>
+      </c>
+      <c r="G23" s="5">
+        <v>2751</v>
+      </c>
+      <c r="H23" s="5">
+        <v>2719</v>
+      </c>
+      <c r="I23" s="5">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="7">
-        <v>3142</v>
-      </c>
-      <c r="C23" s="7">
-        <v>3055</v>
-      </c>
-      <c r="D23" s="7">
-        <v>2976</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2890</v>
-      </c>
-      <c r="F23" s="7">
-        <v>2814</v>
-      </c>
-      <c r="G23" s="7">
-        <v>2751</v>
-      </c>
-      <c r="H23" s="7">
-        <v>2719</v>
-      </c>
-      <c r="I23" s="7">
-        <v>2703</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="B24" s="5">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="7">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="B25" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C25" s="5">
+        <v>983</v>
+      </c>
+      <c r="D25" s="5">
+        <v>959</v>
+      </c>
+      <c r="E25" s="5">
+        <v>931</v>
+      </c>
+      <c r="F25" s="5">
+        <v>917</v>
+      </c>
+      <c r="G25" s="5">
+        <v>908</v>
+      </c>
+      <c r="H25" s="5">
+        <v>888</v>
+      </c>
+      <c r="I25" s="5">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="7">
-        <v>1000</v>
-      </c>
-      <c r="C25" s="7">
-        <v>983</v>
-      </c>
-      <c r="D25" s="7">
-        <v>959</v>
-      </c>
-      <c r="E25" s="7">
-        <v>931</v>
-      </c>
-      <c r="F25" s="7">
-        <v>917</v>
-      </c>
-      <c r="G25" s="7">
-        <v>908</v>
-      </c>
-      <c r="H25" s="7">
-        <v>888</v>
-      </c>
-      <c r="I25" s="7">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="14">
+      <c r="B26" s="12">
         <f t="shared" ref="B26:I26" si="4">SUM(B23:B25)</f>
         <v>4142</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="12">
         <f t="shared" si="4"/>
         <v>4038</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <f t="shared" si="4"/>
         <v>3935</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="12">
         <f t="shared" si="4"/>
         <v>3821</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="12">
         <f t="shared" si="4"/>
         <v>3731</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="12">
         <f t="shared" si="4"/>
         <v>3659</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="12">
         <f t="shared" si="4"/>
         <v>3607</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="12">
         <f t="shared" si="4"/>
         <v>3573</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>27</v>
+      <c r="A27" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2981,228 +5045,228 @@
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5">
+        <v>160962</v>
+      </c>
+      <c r="C28" s="5">
+        <v>158279</v>
+      </c>
+      <c r="D28" s="5">
+        <v>156759</v>
+      </c>
+      <c r="E28" s="5">
+        <v>153939</v>
+      </c>
+      <c r="F28" s="5">
+        <v>149806</v>
+      </c>
+      <c r="G28" s="5">
+        <v>145739</v>
+      </c>
+      <c r="H28" s="5">
+        <v>144464</v>
+      </c>
+      <c r="I28" s="5">
+        <v>142700</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="7">
-        <v>160962</v>
-      </c>
-      <c r="C28" s="7">
-        <v>158279</v>
-      </c>
-      <c r="D28" s="7">
-        <v>156759</v>
-      </c>
-      <c r="E28" s="7">
-        <v>153939</v>
-      </c>
-      <c r="F28" s="7">
-        <v>149806</v>
-      </c>
-      <c r="G28" s="7">
-        <v>145739</v>
-      </c>
-      <c r="H28" s="7">
-        <v>144464</v>
-      </c>
-      <c r="I28" s="7">
-        <v>142700</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="B29" s="5">
+        <v>18258</v>
+      </c>
+      <c r="C29" s="5">
+        <v>17945</v>
+      </c>
+      <c r="D29" s="5">
+        <v>17462</v>
+      </c>
+      <c r="E29" s="5">
+        <v>17182</v>
+      </c>
+      <c r="F29" s="5">
+        <v>16679</v>
+      </c>
+      <c r="G29" s="5">
+        <v>16304</v>
+      </c>
+      <c r="H29" s="5">
+        <v>16012</v>
+      </c>
+      <c r="I29" s="5">
+        <v>15718</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="7">
-        <v>18258</v>
-      </c>
-      <c r="C29" s="7">
-        <v>17945</v>
-      </c>
-      <c r="D29" s="7">
-        <v>17462</v>
-      </c>
-      <c r="E29" s="7">
-        <v>17182</v>
-      </c>
-      <c r="F29" s="7">
-        <v>16679</v>
-      </c>
-      <c r="G29" s="7">
-        <v>16304</v>
-      </c>
-      <c r="H29" s="7">
-        <v>16012</v>
-      </c>
-      <c r="I29" s="7">
-        <v>15718</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="B30" s="5">
+        <v>7061</v>
+      </c>
+      <c r="C30" s="5">
+        <v>6966</v>
+      </c>
+      <c r="D30" s="5">
+        <v>6800</v>
+      </c>
+      <c r="E30" s="5">
+        <v>6729</v>
+      </c>
+      <c r="F30" s="5">
+        <v>6667</v>
+      </c>
+      <c r="G30" s="5">
+        <v>6563</v>
+      </c>
+      <c r="H30" s="5">
+        <v>6524</v>
+      </c>
+      <c r="I30" s="5">
+        <v>6369</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="7">
-        <v>7061</v>
-      </c>
-      <c r="C30" s="7">
-        <v>6966</v>
-      </c>
-      <c r="D30" s="7">
-        <v>6800</v>
-      </c>
-      <c r="E30" s="7">
-        <v>6729</v>
-      </c>
-      <c r="F30" s="7">
-        <v>6667</v>
-      </c>
-      <c r="G30" s="7">
-        <v>6563</v>
-      </c>
-      <c r="H30" s="7">
-        <v>6524</v>
-      </c>
-      <c r="I30" s="7">
-        <v>6369</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B31" s="5">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="7">
-        <v>0</v>
-      </c>
-      <c r="C31" s="7">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0</v>
-      </c>
-      <c r="F31" s="7">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7">
-        <v>0</v>
-      </c>
-      <c r="H31" s="7">
-        <v>0</v>
-      </c>
-      <c r="I31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="14">
+      <c r="B32" s="12">
         <f t="shared" ref="B32:I32" si="5">SUM(B28:B31)</f>
         <v>186281</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="12">
         <f t="shared" si="5"/>
         <v>183190</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <f t="shared" si="5"/>
         <v>181021</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="12">
         <f t="shared" si="5"/>
         <v>177850</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f t="shared" si="5"/>
         <v>173152</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="12">
         <f t="shared" si="5"/>
         <v>168606</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="12">
         <f t="shared" si="5"/>
         <v>167000</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="12">
         <f t="shared" si="5"/>
         <v>164787</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="14">
+      <c r="A33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="12">
         <f t="shared" ref="B33:I33" si="6">B26+B32</f>
         <v>190423</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="12">
         <f t="shared" si="6"/>
         <v>187228</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <f t="shared" si="6"/>
         <v>184956</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="12">
         <f t="shared" si="6"/>
         <v>181671</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f t="shared" si="6"/>
         <v>176883</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="12">
         <f t="shared" si="6"/>
         <v>172265</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="12">
         <f t="shared" si="6"/>
         <v>170607</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="12">
         <f t="shared" si="6"/>
         <v>168360</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="9">
+      <c r="A34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7">
         <f t="shared" ref="B34:I34" si="7">B21-B33</f>
         <v>252468</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="7">
         <f t="shared" si="7"/>
         <v>258335</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="7">
         <f t="shared" si="7"/>
         <v>265061</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="7">
         <f t="shared" si="7"/>
         <v>277360</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="7">
         <f t="shared" si="7"/>
         <v>288098</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="7">
         <f t="shared" si="7"/>
         <v>298893</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="7">
         <f t="shared" si="7"/>
         <v>306583</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="7">
         <f t="shared" si="7"/>
         <v>317522</v>
       </c>
@@ -3219,73 +5283,73 @@
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="15">
+      <c r="A36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="13">
         <v>0</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="13">
         <f t="shared" ref="C36:I36" si="8">C34-B34</f>
         <v>5867</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="13">
         <f t="shared" si="8"/>
         <v>6726</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="13">
         <f t="shared" si="8"/>
         <v>12299</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="13">
         <f t="shared" si="8"/>
         <v>10738</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="13">
         <f t="shared" si="8"/>
         <v>10795</v>
       </c>
-      <c r="H36" s="15">
+      <c r="H36" s="13">
         <f t="shared" si="8"/>
         <v>7690</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="13">
         <f t="shared" si="8"/>
         <v>10939</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="16">
+      <c r="A37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="14">
         <v>0</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="14">
         <f t="shared" ref="C37:I37" si="9">IFERROR(C36/B34,0)</f>
         <v>2.3238588652819366E-2</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="14">
         <f t="shared" si="9"/>
         <v>2.6035961058315751E-2</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="14">
         <f t="shared" si="9"/>
         <v>4.6400639852713151E-2</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="14">
         <f t="shared" si="9"/>
         <v>3.8715027401211424E-2</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="14">
         <f t="shared" si="9"/>
         <v>3.7469888718422203E-2</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="14">
         <f t="shared" si="9"/>
         <v>2.5728270652039358E-2</v>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="14">
         <f t="shared" si="9"/>
         <v>3.5680386714201373E-2</v>
       </c>
@@ -3302,260 +5366,258 @@
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="4" max="6" width="13" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>47</v>
+      <c r="A2" s="15" t="s">
+        <v>46</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="5">
+        <v>7200</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="7">
-        <v>7200</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="B4" s="5">
+        <v>3800</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="7">
-        <v>3800</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="B5" s="5">
+        <v>350</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="7">
-        <v>350</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>1200</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="C8" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="20" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="21">
-        <f>'Balance Sheet'!B7/B4</f>
+      <c r="B9" s="17">
+        <f>'Balance Sheet'!B6/B4</f>
         <v>5.641578947368421</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="17">
         <f>IFERROR('Quarterly History'!H7/B4,0)</f>
         <v>5.5310526315789472</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="25">
         <f t="shared" ref="D9:D14" si="0">B9-C9</f>
         <v>0.11052631578947381</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="18" t="str">
+      <c r="E9" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="26" t="str">
         <f>IF(B9&gt;3,"Healthy",IF(B9&gt;1.79999999999999,"Watch","Concern"))</f>
         <v>Healthy</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="21">
-        <f>'Balance Sheet'!B33/'Balance Sheet'!B21</f>
+      <c r="A10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="17">
+        <f>'Balance Sheet'!B32/'Balance Sheet'!B20</f>
         <v>0.34650388365899537</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="17">
         <f>IFERROR('Quarterly History'!H33/'Quarterly History'!H21,0)</f>
         <v>0.35752425658542719</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="25">
         <f t="shared" si="0"/>
         <v>-1.1020372926431821E-2</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="18" t="str">
+      <c r="E10" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="26" t="str">
         <f>IF(B10&lt;0.5,"Healthy",IF(B10&lt;0.65,"Watch","Concern"))</f>
         <v>Healthy</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="21">
-        <f>'Balance Sheet'!B34/'Balance Sheet'!B21</f>
+      <c r="A11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="17">
+        <f>'Balance Sheet'!B33/'Balance Sheet'!B20</f>
         <v>0.65349611634100457</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="17">
         <f>IFERROR('Quarterly History'!H34/'Quarterly History'!H21,0)</f>
         <v>0.64247574341457281</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="25">
         <f t="shared" si="0"/>
         <v>1.1020372926431765E-2</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="18" t="str">
+      <c r="E11" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="26" t="str">
         <f>IF(B11&gt;0.5,"Healthy",IF(B11&gt;0.3,"Watch","Concern"))</f>
         <v>Healthy</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="16">
+      <c r="A12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="14">
         <f>B6/B3</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <f>B6/B3</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="18" t="str">
+      <c r="E12" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="26" t="str">
         <f>IF(B12&gt;0.15,"Healthy",IF(B12&gt;0.09,"Watch","Concern"))</f>
         <v>Healthy</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="21">
-        <f>'Balance Sheet'!B15/'Balance Sheet'!B21</f>
+      <c r="A13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="17">
+        <f>'Balance Sheet'!B14/'Balance Sheet'!B20</f>
         <v>0.3177932090507572</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="17">
         <f>IFERROR('Quarterly History'!H15/'Quarterly History'!H21,0)</f>
         <v>0.31680253148641002</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="25">
         <f t="shared" si="0"/>
         <v>9.9067756434717547E-4</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="18" t="str">
+      <c r="E13" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="26" t="str">
         <f>IF(B13&gt;0.3,"Healthy",IF(B13&gt;0.18,"Watch","Concern"))</f>
         <v>Healthy</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="21">
-        <f>('Balance Sheet'!B28/12+B5)/B3</f>
+      <c r="A14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="17">
+        <f>('Balance Sheet'!B27/12+B5)/B3</f>
         <v>1.7002314814814814</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="17">
         <f>IFERROR(('Quarterly History'!H28/12+B5)/B3,0)</f>
         <v>1.7206481481481481</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="25">
         <f t="shared" si="0"/>
         <v>-2.041666666666675E-2</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="18" t="str">
+      <c r="E14" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="26" t="str">
         <f>IF(B14&lt;0.28,"Healthy",IF(B14&lt;0.364,"Watch","Concern"))</f>
         <v>Concern</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F9:F14">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Healthy"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Watch"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Concern"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3577,7 +5639,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3586,496 +5648,496 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="15">
+      <c r="A3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="13">
         <f>'Quarterly History'!H4</f>
         <v>4782</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="13">
         <f>'Quarterly History'!I4</f>
         <v>4820</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="13">
         <f t="shared" ref="D3:D14" si="0">C3-B3</f>
         <v>38</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="14">
         <f t="shared" ref="E3:E21" si="1">IFERROR(D3/ABS(B3),0)</f>
         <v>7.9464659138435804E-3</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="14">
         <f t="shared" ref="F3:F21" si="2">IFERROR(D3/$D$23,0)</f>
         <v>3.4738093061522993E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="13">
         <f>'Quarterly History'!H5</f>
         <v>12891</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <f>'Quarterly History'!I5</f>
         <v>13204</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="13">
         <f t="shared" si="0"/>
         <v>313</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="14">
         <f t="shared" si="1"/>
         <v>2.4280505779225817E-2</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="14">
         <f t="shared" si="2"/>
         <v>2.8613218758570255E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="13">
         <f>'Quarterly History'!H6</f>
         <v>3345</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="13">
         <f>'Quarterly History'!I6</f>
         <v>3414</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <f t="shared" si="1"/>
         <v>2.062780269058296E-2</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="14">
         <f t="shared" si="2"/>
         <v>6.307706371697596E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="13">
         <f>'Quarterly History'!H9</f>
         <v>35180</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <f>'Quarterly History'!I9</f>
         <v>35625</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <f t="shared" si="0"/>
         <v>445</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <f t="shared" si="1"/>
         <v>1.2649232518476407E-2</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="14">
         <f t="shared" si="2"/>
         <v>4.068013529573087E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="13">
         <f>'Quarterly History'!H10</f>
         <v>71317</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <f>'Quarterly History'!I10</f>
         <v>72764</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <f t="shared" si="0"/>
         <v>1447</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="14">
         <f t="shared" si="1"/>
         <v>2.0289692499684507E-2</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="14">
         <f t="shared" si="2"/>
         <v>0.13227900173690466</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="13">
         <f>'Quarterly History'!H11</f>
         <v>28904</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <f>'Quarterly History'!I11</f>
         <v>29834</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <f t="shared" si="0"/>
         <v>930</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <f t="shared" si="1"/>
         <v>3.2175477442568504E-2</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="14">
         <f t="shared" si="2"/>
         <v>8.5016911966358896E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="13">
         <f>'Quarterly History'!H12</f>
         <v>5734</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <f>'Quarterly History'!I12</f>
         <v>5865</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="13">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="14">
         <f t="shared" si="1"/>
         <v>2.2846180676665506E-2</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="14">
         <f t="shared" si="2"/>
         <v>1.197550050278819E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="13">
         <f>'Quarterly History'!H13</f>
         <v>7179</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <f>'Quarterly History'!I13</f>
         <v>7395</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="14">
         <f t="shared" si="1"/>
         <v>3.0087755954868366E-2</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="14">
         <f t="shared" si="2"/>
         <v>1.9745863424444648E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="15">
+      <c r="A11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="13">
         <f>'Quarterly History'!H14</f>
         <v>2861</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <f>'Quarterly History'!I14</f>
         <v>2927</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="14">
         <f t="shared" si="1"/>
         <v>2.3068857042991962E-2</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="14">
         <f t="shared" si="2"/>
         <v>6.0334582685803093E-3</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="15">
+      <c r="A12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="13">
         <f>'Quarterly History'!H17</f>
         <v>284273</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <f>'Quarterly History'!I17</f>
         <v>289539</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="13">
         <f t="shared" si="0"/>
         <v>5266</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="14">
         <f t="shared" si="1"/>
         <v>1.8524446570726029E-2</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="14">
         <f t="shared" si="2"/>
         <v>0.48139683700521069</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="15">
+      <c r="A13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="13">
         <f>'Quarterly History'!H18</f>
         <v>13388</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <f>'Quarterly History'!I18</f>
         <v>12989</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <f t="shared" si="0"/>
         <v>-399</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="14">
         <f t="shared" si="1"/>
         <v>-2.9802808485210636E-2</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="14">
         <f t="shared" si="2"/>
         <v>-3.6474997714599139E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="15">
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="13">
         <f>'Quarterly History'!H19</f>
         <v>7336</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="13">
         <f>'Quarterly History'!I19</f>
         <v>7506</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="14">
         <f t="shared" si="1"/>
         <v>2.3173391494002181E-2</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="14">
         <f t="shared" si="2"/>
         <v>1.5540725843312918E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="13">
         <f>'Quarterly History'!H23</f>
         <v>2719</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <f>'Quarterly History'!I23</f>
         <v>2703</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13">
         <f t="shared" ref="D15:D21" si="3">B15-C15</f>
         <v>16</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="14">
         <f t="shared" si="1"/>
         <v>5.884516366311144E-3</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="14">
         <f t="shared" si="2"/>
         <v>1.4626565499588629E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="13">
         <f>'Quarterly History'!H24</f>
         <v>0</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <f>'Quarterly History'!I24</f>
         <v>0</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="13">
         <f>'Quarterly History'!H25</f>
         <v>888</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13">
         <f>'Quarterly History'!I25</f>
         <v>870</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="13">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="14">
         <f t="shared" si="1"/>
         <v>2.0270270270270271E-2</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="14">
         <f t="shared" si="2"/>
         <v>1.6454886187037207E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="13">
         <f>'Quarterly History'!H28</f>
         <v>144464</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13">
         <f>'Quarterly History'!I28</f>
         <v>142700</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="13">
         <f t="shared" si="3"/>
         <v>1764</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="14">
         <f t="shared" si="1"/>
         <v>1.2210654557536825E-2</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="14">
         <f t="shared" si="2"/>
         <v>0.16125788463296462</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="13">
         <f>'Quarterly History'!H29</f>
         <v>16012</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="13">
         <f>'Quarterly History'!I29</f>
         <v>15718</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="13">
         <f t="shared" si="3"/>
         <v>294</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="14">
         <f t="shared" si="1"/>
         <v>1.8361229078191356E-2</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="14">
         <f t="shared" si="2"/>
         <v>2.6876314105494105E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="15">
+      <c r="A20" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="13">
         <f>'Quarterly History'!H30</f>
         <v>6524</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <f>'Quarterly History'!I30</f>
         <v>6369</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="14">
         <f t="shared" si="1"/>
         <v>2.3758430410790926E-2</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="14">
         <f t="shared" si="2"/>
         <v>1.4169485327726484E-2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="13">
         <f>'Quarterly History'!H31</f>
         <v>0</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <f>'Quarterly History'!I31</f>
         <v>0</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4089,17 +6151,17 @@
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="14">
+      <c r="A23" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="29">
         <f>'Quarterly History'!I34-'Quarterly History'!H34</f>
         <v>10939</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4108,45 +6170,45 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" style="34" customWidth="1"/>
     <col min="3" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="B1" s="32"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="2"/>
+      <c r="A2" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="32"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>79</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="31">
         <f>'Quarterly History'!B34</f>
         <v>252468</v>
       </c>
@@ -4154,10 +6216,10 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="31">
         <f>'Quarterly History'!C34</f>
         <v>258335</v>
       </c>
@@ -4165,10 +6227,10 @@
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="31">
         <f>'Quarterly History'!D34</f>
         <v>265061</v>
       </c>
@@ -4176,10 +6238,10 @@
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="31">
         <f>'Quarterly History'!E34</f>
         <v>277360</v>
       </c>
@@ -4187,10 +6249,10 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="31">
         <f>'Quarterly History'!F34</f>
         <v>288098</v>
       </c>
@@ -4198,10 +6260,10 @@
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="31">
         <f>'Quarterly History'!G34</f>
         <v>298893</v>
       </c>
@@ -4209,10 +6271,10 @@
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="31">
         <f>'Quarterly History'!H34</f>
         <v>306583</v>
       </c>
@@ -4220,10 +6282,10 @@
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="15">
+      <c r="A11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="31">
         <f>'Quarterly History'!I34</f>
         <v>317522</v>
       </c>
@@ -4232,510 +6294,495 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="31">
         <f>'Quarterly History'!B7</f>
         <v>19575</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="31">
         <f>'Quarterly History'!B15</f>
         <v>132106</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="31">
         <f>'Quarterly History'!B20</f>
         <v>291210</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="31">
         <f>'Quarterly History'!C7</f>
         <v>19676</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="31">
         <f>'Quarterly History'!C15</f>
         <v>134925</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="31">
         <f>'Quarterly History'!C20</f>
         <v>290962</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="31">
         <f>'Quarterly History'!D7</f>
         <v>19840</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="31">
         <f>'Quarterly History'!D15</f>
         <v>138354</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="31">
         <f>'Quarterly History'!D20</f>
         <v>291823</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="31">
         <f>'Quarterly History'!E7</f>
         <v>20168</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="31">
         <f>'Quarterly History'!E15</f>
         <v>141381</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="31">
         <f>'Quarterly History'!E20</f>
         <v>297482</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="31">
         <f>'Quarterly History'!F7</f>
         <v>20598</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="31">
         <f>'Quarterly History'!F15</f>
         <v>144138</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="31">
         <f>'Quarterly History'!F20</f>
         <v>300245</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="15">
+      <c r="A20" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="31">
         <f>'Quarterly History'!G7</f>
         <v>20890</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="31">
         <f>'Quarterly History'!G15</f>
         <v>147543</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="31">
         <f>'Quarterly History'!G20</f>
         <v>302725</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="31">
         <f>'Quarterly History'!H7</f>
         <v>21018</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="31">
         <f>'Quarterly History'!H15</f>
         <v>151175</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="31">
         <f>'Quarterly History'!H20</f>
         <v>304997</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="15">
+      <c r="A22" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="31">
         <f>'Quarterly History'!I7</f>
         <v>21438</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="31">
         <f>'Quarterly History'!I15</f>
         <v>154410</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="31">
         <f>'Quarterly History'!I20</f>
         <v>310034</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="32"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="A24" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>52</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+      <c r="A25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="33">
+        <f>Ratios!B9</f>
+        <v>5.641578947368421</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="A26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="33">
+        <f>Ratios!B10</f>
+        <v>0.34650388365899537</v>
+      </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="A27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="33">
+        <f>Ratios!B11</f>
+        <v>0.65349611634100457</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+      <c r="A28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="33">
+        <f>Ratios!B12</f>
+        <v>0.16666666666666666</v>
+      </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+      <c r="A29" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="33">
+        <f>Ratios!B13</f>
+        <v>0.3177932090507572</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+      <c r="A30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="33">
+        <f>Ratios!B14</f>
+        <v>1.7002314814814814</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="32"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="32"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+      <c r="B35" s="32"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
+      <c r="B37" s="32"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
+      <c r="B38" s="32"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="B39" s="32"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="21">
-        <f>Ratios!B9</f>
-        <v>5.641578947368421</v>
-      </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="21">
-        <f>Ratios!B10</f>
-        <v>0.34650388365899537</v>
-      </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="21">
-        <f>Ratios!B11</f>
-        <v>0.65349611634100457</v>
-      </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" s="21">
-        <f>Ratios!B12</f>
-        <v>0.16666666666666666</v>
-      </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="21">
-        <f>Ratios!B13</f>
-        <v>0.3177932090507572</v>
-      </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" s="21">
-        <f>Ratios!B14</f>
-        <v>1.7002314814814814</v>
-      </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
+      <c r="B48" s="32"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="32"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="B50" s="32"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="32"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="B52" s="32"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
+      <c r="B53" s="32"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
+      <c r="B54" s="32"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
+      <c r="B55" s="32"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="32"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="32"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="32"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="32"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
+      <c r="B60" s="32"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
+      <c r="B61" s="32"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="32"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="32"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="A64" s="2"/>
+      <c r="B64" s="32"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="15">
-        <f>'Quarterly History'!I7-'Quarterly History'!H7</f>
-        <v>420</v>
-      </c>
+      <c r="A65" s="2"/>
+      <c r="B65" s="32"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B66" s="15">
-        <f>'Quarterly History'!I15-'Quarterly History'!H15</f>
-        <v>3235</v>
-      </c>
+      <c r="A66" s="2"/>
+      <c r="B66" s="32"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B67" s="15">
-        <f>'Quarterly History'!I20-'Quarterly History'!H20</f>
-        <v>5037</v>
-      </c>
+      <c r="A67" s="2"/>
+      <c r="B67" s="32"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" s="15">
-        <f>'Quarterly History'!I26-'Quarterly History'!H26</f>
-        <v>-34</v>
-      </c>
+      <c r="A68" s="2"/>
+      <c r="B68" s="32"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" s="15">
-        <f>'Quarterly History'!I32-'Quarterly History'!H32</f>
-        <v>-2213</v>
-      </c>
+      <c r="A69" s="2"/>
+      <c r="B69" s="32"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4752,48 +6799,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
